--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136940958</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>136940838</v>
       </c>
       <c r="B4" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136940958</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>136940838</v>
       </c>
       <c r="B4" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -841,11 +837,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -989,11 +981,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1215,11 +1203,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136940958</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136940838</v>
       </c>
       <c r="B4" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136940958</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136940838</v>
       </c>
       <c r="B4" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136940958</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96769</v>
+        <v>96770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108474</v>
+        <v>108476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35180-2026 artfynd.xlsx
+++ b/artfynd/A 35180-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136940788</v>
       </c>
       <c r="B2" t="n">
-        <v>96770</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136940958</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>136940838</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>136940996</v>
       </c>
       <c r="B5" t="n">
-        <v>108476</v>
+        <v>108480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>136940836</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
